--- a/results/YUYU样本量变化.xlsx
+++ b/results/YUYU样本量变化.xlsx
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>5.5</v>
+        <v>5.54</v>
       </c>
     </row>
   </sheetData>

--- a/results/YUYU样本量变化.xlsx
+++ b/results/YUYU样本量变化.xlsx
@@ -470,7 +470,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>455</v>
+        <v>460</v>
       </c>
     </row>
     <row r="3">
@@ -485,7 +485,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4">
@@ -500,7 +500,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>449</v>
+        <v>436</v>
       </c>
     </row>
     <row r="5">
@@ -545,7 +545,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>449</v>
+        <v>412</v>
       </c>
     </row>
     <row r="8">
@@ -560,7 +560,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>451</v>
+        <v>419</v>
       </c>
     </row>
     <row r="9">
@@ -575,7 +575,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10">
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>444</v>
+        <v>400</v>
       </c>
     </row>
     <row r="11">
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>444</v>
+        <v>373</v>
       </c>
     </row>
     <row r="13">
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>441</v>
+        <v>376</v>
       </c>
     </row>
     <row r="14">
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15">
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>438</v>
+        <v>362</v>
       </c>
     </row>
     <row r="16">
@@ -680,7 +680,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>85</v>
+        <v>79</v>
       </c>
     </row>
     <row r="17">
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>438</v>
+        <v>362</v>
       </c>
     </row>
     <row r="21">
@@ -770,7 +770,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>438</v>
+        <v>362</v>
       </c>
     </row>
     <row r="23">
@@ -785,7 +785,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>438</v>
+        <v>362</v>
       </c>
     </row>
     <row r="24">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>5.54</v>
+        <v>4.58</v>
       </c>
     </row>
   </sheetData>

--- a/results/YUYU样本量变化.xlsx
+++ b/results/YUYU样本量变化.xlsx
@@ -545,7 +545,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="8">
@@ -560,7 +560,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="9">
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="11">
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="13">
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
     <row r="14">
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="16">
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="21">
@@ -770,7 +770,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="23">
@@ -785,7 +785,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="24">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>4.58</v>
+        <v>4.56</v>
       </c>
     </row>
   </sheetData>

--- a/results/YUYU样本量变化.xlsx
+++ b/results/YUYU样本量变化.xlsx
@@ -485,7 +485,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4">
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="13">
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="14">
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="16">
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="21">
@@ -770,7 +770,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="23">
@@ -785,7 +785,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="24">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>4.56</v>
+        <v>4.57</v>
       </c>
     </row>
   </sheetData>

--- a/results/YUYU样本量变化.xlsx
+++ b/results/YUYU样本量变化.xlsx
@@ -485,7 +485,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4">
@@ -500,7 +500,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="5">
@@ -545,7 +545,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>413</v>
+        <v>409</v>
       </c>
     </row>
     <row r="8">
@@ -560,7 +560,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>420</v>
+        <v>416</v>
       </c>
     </row>
     <row r="9">
@@ -575,7 +575,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10">
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>401</v>
+        <v>395</v>
       </c>
     </row>
     <row r="11">
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>372</v>
+        <v>367</v>
       </c>
     </row>
     <row r="13">
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>375</v>
+        <v>370</v>
       </c>
     </row>
     <row r="14">
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15">
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>361</v>
+        <v>354</v>
       </c>
     </row>
     <row r="16">
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>361</v>
+        <v>354</v>
       </c>
     </row>
     <row r="21">
@@ -770,7 +770,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>361</v>
+        <v>354</v>
       </c>
     </row>
     <row r="23">
@@ -785,7 +785,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>361</v>
+        <v>354</v>
       </c>
     </row>
     <row r="24">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>4.57</v>
+        <v>4.48</v>
       </c>
     </row>
   </sheetData>

--- a/results/YUYU样本量变化.xlsx
+++ b/results/YUYU样本量变化.xlsx
@@ -3,45 +3,393 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="13545" windowHeight="12255" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
+  <fonts count="21">
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="12"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <b val="1"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C6500"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color theme="0"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="36">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -51,33 +399,551 @@
     </border>
     <border>
       <left style="thin">
-        <color auto="1"/>
+        <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
-        <color auto="1"/>
+        <color rgb="FFB2B2B2"/>
       </right>
       <top style="thin">
-        <color auto="1"/>
+        <color rgb="FFB2B2B2"/>
       </top>
       <bottom style="thin">
-        <color auto="1"/>
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="49">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="35" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="11">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <dxfs count="17">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="double">
+          <color theme="4"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <left style="thin">
+          <color theme="4"/>
+        </left>
+        <right style="thin">
+          <color theme="4"/>
+        </right>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+        <horizontal style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+  </dxfs>
+  <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7">
+      <tableStyleElement type="wholeTable" dxfId="6"/>
+      <tableStyleElement type="headerRow" dxfId="5"/>
+      <tableStyleElement type="totalRow" dxfId="4"/>
+      <tableStyleElement type="firstColumn" dxfId="3"/>
+      <tableStyleElement type="lastColumn" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+    </tableStyle>
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10">
+      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="totalRow" dxfId="15"/>
+      <tableStyleElement type="firstRowStripe" dxfId="14"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
+      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+    </tableStyle>
+  </tableStyles>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -150,9 +1016,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="WPS">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="WPS">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -160,39 +1026,39 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="4874CB"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="EE822F"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="F2BA02"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="75BD42"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="30C0B4"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="E54C5E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0026E5"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="7E1FAD"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="WPS">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -224,6 +1090,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -258,177 +1125,140 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="WPS">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="35000">
-              <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
+                <a:lumOff val="17500"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
+              <a:schemeClr val="phClr"/>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin ang="2700000" scaled="0"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
+                <a:hueOff val="-2520000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
-              </a:schemeClr>
+              <a:schemeClr val="phClr"/>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin ang="2700000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:gradFill>
+            <a:gsLst>
+              <a:gs pos="0">
+                <a:schemeClr val="phClr">
+                  <a:hueOff val="-4200000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="100000">
+                <a:schemeClr val="phClr"/>
+              </a:gs>
+            </a:gsLst>
+            <a:lin ang="2700000" scaled="1"/>
+          </a:gradFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
-              </a:srgbClr>
+            <a:outerShdw blurRad="101600" dist="50800" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:schemeClr val="phClr">
+                <a:alpha val="60000"/>
+              </a:schemeClr>
             </a:outerShdw>
           </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
+            <a:reflection stA="50000" endA="300" endPos="40000" dist="25400" dir="5400000" sy="-100000" algn="bl" rotWithShape="0"/>
           </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
+                <a:alpha val="63000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="40000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -438,10 +1268,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C26"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:D34"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
+  <cols>
+    <col width="25.5" customWidth="1" style="10" min="1" max="1"/>
+    <col width="19.625" customWidth="1" style="10" min="2" max="2"/>
+    <col width="19.5" customWidth="1" style="10" min="3" max="3"/>
+    <col width="35.5" customWidth="1" style="10" min="4" max="4"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="14.25" customHeight="1" s="10">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>模块</t>
@@ -457,383 +1293,580 @@
           <t>你的数字</t>
         </is>
       </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>备注/定义</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="C2" s="2" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>B. T1下属端</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B3" s="9" t="inlineStr">
         <is>
           <t>T1提交问卷下属数</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="C3" s="4" t="n">
         <v>460</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>实际提交T1问卷的人数（未清洗前）</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>B. T1下属端</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>T1注意力检查失败人数</t>
         </is>
       </c>
-      <c r="C3" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="C4" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>按你预先设定规则判定</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>B. T1下属端</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>T1可用下属数</t>
         </is>
       </c>
-      <c r="C4" t="n">
+      <c r="C5" s="8" t="n">
         <v>434</v>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>T1最终保留的follower数</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>B. T1下属端</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>T1可用团队数</t>
         </is>
       </c>
-      <c r="C5" t="n">
+      <c r="C6" s="8" t="n">
         <v>90</v>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>T1可用下属所对应的team数</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>B. T1下属端</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>T1可用领导数</t>
         </is>
       </c>
-      <c r="C6" t="n">
+      <c r="C7" s="8" t="n">
         <v>90</v>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>T1可用下属所对应的leader数</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="C8" s="2" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>C. T2下属端</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B9" s="9" t="inlineStr">
         <is>
           <t>T2受邀下属数</t>
         </is>
       </c>
-      <c r="C7" t="n">
+      <c r="C9" s="4" t="n">
         <v>409</v>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>通常=T1可用下属数</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>C. T2下属端</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B10" s="9" t="inlineStr">
         <is>
           <t>T2提交问卷下属数</t>
         </is>
       </c>
-      <c r="C8" t="n">
+      <c r="C10" s="4" t="n">
         <v>416</v>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>实际提交T2问卷的人数（未清洗前）</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>C. T2下属端</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>T2注意力检查失败人数</t>
         </is>
       </c>
-      <c r="C9" t="n">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="C11" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="D11" s="5" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>C. T2下属端</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B12" s="7" t="inlineStr">
         <is>
           <t>T2可用下属数</t>
         </is>
       </c>
-      <c r="C10" t="n">
+      <c r="C12" s="8" t="n">
         <v>395</v>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>T2最终保留的follower数</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>C. T2下属端</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>T2可用团队数</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="n">
+        <v>85</v>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>T2可用下属所对应的team数</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>C. T2下属端</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>T2可用领导数</t>
         </is>
       </c>
-      <c r="C11" t="n">
+      <c r="C14" s="8" t="n">
         <v>85</v>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>T2可用下属所对应的leader数</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" s="2" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
         <is>
           <t>D. T3下属端</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B16" s="9" t="inlineStr">
         <is>
           <t>T3受邀下属数</t>
         </is>
       </c>
-      <c r="C12" t="n">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="C16" s="4" t="n">
+        <v>369</v>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>通常=T2可用下属数</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr">
         <is>
           <t>D. T3下属端</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B17" s="9" t="inlineStr">
         <is>
           <t>T3提交问卷下属数</t>
         </is>
       </c>
-      <c r="C13" t="n">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C17" s="4" t="n">
+        <v>372</v>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>实际提交T3下属端问卷人数（未清洗前）</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>D. T3下属端</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>T3下属注意力检查失败人数</t>
         </is>
       </c>
-      <c r="C14" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="C18" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="D18" s="5" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>D. T3下属端</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B19" s="7" t="inlineStr">
         <is>
           <t>T3下属可用人数</t>
         </is>
       </c>
-      <c r="C15" t="n">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="C19" s="8" t="n">
+        <v>356</v>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>T3 follower端最终保留人数</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" s="2" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="9" t="inlineStr">
         <is>
           <t>E. T3领导端</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B21" s="9" t="inlineStr">
         <is>
           <t>T3受邀领导数</t>
         </is>
       </c>
-      <c r="C16" t="n">
+      <c r="C21" s="4" t="n">
         <v>79</v>
       </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>被邀请填写T3领导端问卷的leader数.在 T2 清洗完成后，所有“有资格进入 T3 的 follower”所对应的独立 LeaderID 数量。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="inlineStr">
         <is>
           <t>E. T3领导端</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B22" s="9" t="inlineStr">
         <is>
           <t>T3提交问卷领导数</t>
         </is>
       </c>
-      <c r="C17" t="n">
+      <c r="C22" s="4" t="n">
         <v>81</v>
       </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>实际提交T3领导端问卷人数（未清洗前）</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>E. T3领导端</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>T3领导注意力检查失败人数</t>
         </is>
       </c>
-      <c r="C18" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="C23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>如有</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
         <is>
           <t>E. T3领导端</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B24" s="7" t="inlineStr">
         <is>
           <t>T3领导可用人数</t>
         </is>
       </c>
-      <c r="C19" t="n">
+      <c r="C24" s="8" t="n">
         <v>79</v>
       </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>T3 leader端最终保留人数</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>E. T3领导端</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>T3领导可用团队数</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="n">
+        <v>79</v>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>通常≈T3领导可用人数（若一队一领导）</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="C26" s="2" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="0" t="inlineStr">
         <is>
           <t>F. 匹配与最终分析</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>T3两端都回收且ID能初步对上的dyad数</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="B27" s="0" t="inlineStr">
+        <is>
+          <t>T3初步匹配成功的follower-leader dyad数</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="n">
+        <v>356</v>
+      </c>
+      <c r="D27" s="0" t="inlineStr">
+        <is>
+          <t>T3两端都回收且ID能初步对上的dyad数（清洗前）</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="0" t="inlineStr">
         <is>
           <t>F. 匹配与最终分析</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B28" s="0" t="inlineStr">
+        <is>
+          <t>因注意力检查失败剔除的dyad数</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="0" t="inlineStr">
         <is>
           <t>任一关键波次失败且按规则整体剔除</t>
         </is>
       </c>
-      <c r="C21" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+    </row>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
         <is>
           <t>F. 匹配与最终分析</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>最终有效dyad数</t>
+        </is>
+      </c>
+      <c r="C29" s="8" t="n">
+        <v>356</v>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
         <is>
           <t>最终进入主分析的matched follower-leader cases</t>
         </is>
       </c>
-      <c r="C22" t="n">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
         <is>
           <t>F. 匹配与最终分析</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B30" s="7" t="inlineStr">
         <is>
           <t>最终有效下属数</t>
         </is>
       </c>
-      <c r="C23" t="n">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="C30" s="8" t="n">
+        <v>356</v>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>通常=最终有效dyad数</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="7" t="inlineStr">
         <is>
           <t>F. 匹配与最终分析</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B31" s="7" t="inlineStr">
         <is>
           <t>最终有效领导数</t>
         </is>
       </c>
-      <c r="C24" t="n">
+      <c r="C31" s="8" t="n">
         <v>79</v>
       </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>最终分析样本中对应的leader数</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="7" t="inlineStr">
         <is>
           <t>F. 匹配与最终分析</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B32" s="7" t="inlineStr">
         <is>
           <t>最终有效团队数</t>
         </is>
       </c>
-      <c r="C25" t="n">
+      <c r="C32" s="8" t="n">
         <v>79</v>
       </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>最终分析样本中对应的team数</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
         <is>
           <t>F. 匹配与最终分析</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>平均下属数(领导)</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>4.48</v>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>最终每位领导平均对应下属数</t>
+        </is>
+      </c>
+      <c r="C33" s="8" t="n">
+        <v>4.51</v>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>可后算：最终有效下属数 ÷ 最终有效领导数</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="inlineStr">
+        <is>
+          <t>F. 匹配与最终分析</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>最终每团队平均下属数</t>
+        </is>
+      </c>
+      <c r="C34" s="8" t="n">
+        <v>4.51</v>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>可后算：最终有效下属数 ÷ 最终有效团队数</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/results/YUYU样本量变化.xlsx
+++ b/results/YUYU样本量变化.xlsx
@@ -1334,7 +1334,7 @@
         </is>
       </c>
       <c r="C4" s="6" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         </is>
       </c>
       <c r="C5" s="8" t="n">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
@@ -1437,7 +1437,7 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D11" s="5" t="n"/>
     </row>
@@ -1473,7 +1473,7 @@
         </is>
       </c>
       <c r="C12" s="8" t="n">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="D17" s="9" t="inlineStr">
         <is>
@@ -1576,7 +1576,7 @@
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D18" s="5" t="n"/>
     </row>
@@ -1592,7 +1592,7 @@
         </is>
       </c>
       <c r="C19" s="8" t="n">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="D27" s="0" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
         </is>
       </c>
       <c r="C29" s="8" t="n">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
@@ -1778,7 +1778,7 @@
         </is>
       </c>
       <c r="C30" s="8" t="n">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         </is>
       </c>
       <c r="C33" s="8" t="n">
-        <v>4.51</v>
+        <v>4.57</v>
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
@@ -1858,7 +1858,7 @@
         </is>
       </c>
       <c r="C34" s="8" t="n">
-        <v>4.51</v>
+        <v>4.57</v>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
